--- a/build/custom-roles-run/CustomRoles_QA-PreRelease-Checklist_2026-07-16.xlsx
+++ b/build/custom-roles-run/CustomRoles_QA-PreRelease-Checklist_2026-07-16.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -616,160 +616,170 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Intended-loss-to-confirm</t>
+          <t>Spec-silent</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Intended-grant-to-confirm</t>
+          <t>Intended-loss-to-confirm</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Coverage-gap</t>
+          <t>Intended-grant-to-confirm</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>Coverage-gap</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
           <t>Env-config</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
+      <c r="B21" s="2" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="n"/>
-    </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TESTRAIL MAPPING (Standing Rule 8)</t>
-        </is>
-      </c>
+      <c r="A22" s="3" t="n"/>
       <c r="B22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Checklist rows mapped to existing TestRail case(s)</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>35</v>
-      </c>
+          <t>TESTRAIL MAPPING (Standing Rule 8)</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>Checklist rows mapped to existing TestRail case(s)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t>Checklist rows with NO existing case (see Coverage Gaps)</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
+      <c r="B25" s="2" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="n"/>
-      <c r="B25" s="2" t="n"/>
-    </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>GROUND-TRUTH LINEAGE (every row traces here)</t>
-        </is>
-      </c>
+      <c r="A26" s="3" t="n"/>
       <c r="B26" s="2" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Source workbook</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx (Full Dual Matrix, 176 dual rows + Pass-11/Pass-12/Approve-Decline/Send to Terminal/Parts-Module/New-WO tabs + Spec-Standing Conformance)</t>
-        </is>
-      </c>
+          <t>GROUND-TRUTH LINEAGE (every row traces here)</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Spec truth table</t>
+          <t>Source workbook</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>build/custom-roles-run/spec-conformance/spec-truth-table.md</t>
+          <t>build/custom-roles-run/Prod-vs-Staging-LIVE-VERIFIED-2026-07-14.xlsx (Full Dual Matrix, 176 dual rows + Pass-11/Pass-12/Approve-Decline/Send to Terminal/Parts-Module/New-WO tabs + Spec-Standing Conformance)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Canonical spec</t>
+          <t>Spec truth table</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>build/custom-roles-spec-update/current-spec-2026-07-15.md</t>
+          <t>build/custom-roles-run/spec-conformance/spec-truth-table.md</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Evidence</t>
+          <t>Canonical spec</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>build/custom-roles-run/live-ui-2026-07-15/ and build/custom-roles-run/live-ui-2026-07-16/</t>
+          <t>build/custom-roles-spec-update/current-spec-2026-07-15.md</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TestRail case source</t>
+          <t>Evidence</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>build/custom-roles-run/cases-2026-07-13/ (filename = C&lt;id&gt;)</t>
+          <t>build/custom-roles-run/live-ui-2026-07-15/ and build/custom-roles-run/live-ui-2026-07-16/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>TestRail case source</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>build/custom-roles-run/cases-2026-07-13/ (filename = C&lt;id&gt;)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t>Generator</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>build/custom-roles-run/gen_qa_prerelease.py (accuracy gate built in)</t>
         </is>
@@ -931,7 +941,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>build/custom-roles-run/live-ui-2026-07-16/ (Pass-12 Send-to-Terminal evidence; SendToTerminal_dialog.png per role)</t>
+          <t>build/custom-roles-run/live-ui-2026-07-15/staging (SendToTerminal_dialog.png set — pixel-observed for the invoicing roles; NONE exists for this role: its staging cell is method-derived, see GAP-08) + build/custom-roles-run/live-ui-2026-07-16/production/_terminal (Pass-12 prod org-gate captures)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -1005,7 +1015,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>build/custom-roles-run/live-ui-2026-07-16/ (Pass-12 Send-to-Terminal evidence; SendToTerminal_dialog.png per role)</t>
+          <t>build/custom-roles-run/live-ui-2026-07-15/staging (SendToTerminal_dialog.png set — pixel-observed for the invoicing roles; NONE exists for this role: its staging cell is method-derived, see GAP-08) + build/custom-roles-run/live-ui-2026-07-16/production/_terminal (Pass-12 prod org-gate captures)</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -1079,7 +1089,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>build/custom-roles-run/live-ui-2026-07-16/ (Pass-12 Send-to-Terminal evidence; SendToTerminal_dialog.png per role)</t>
+          <t>build/custom-roles-run/live-ui-2026-07-15/staging (SendToTerminal_dialog.png set — pixel-observed for the invoicing roles; NONE exists for this role: its staging cell is method-derived, see GAP-08) + build/custom-roles-run/live-ui-2026-07-16/production/_terminal (Pass-12 prod org-gate captures)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1151,7 +1161,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>build/custom-roles-run/live-ui-2026-07-16/staging + /production (Pass-11 AP/AR captures, e.g. production/apar-per-role.json)</t>
+          <t>build/custom-roles-run/live-ui-2026-07-16/production (Pass-11 AP/AR captures: apar-DUAL-verdicts.json + per-role clean_apar.png) + build/custom-roles-run/live-ui-2026-07-15/staging (per-role apar_reports.png + apar-per-role.json)</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4394,7 +4404,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Spec-contradiction</t>
+          <t>Spec-silent</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -4775,7 +4785,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Smoke-only if time permits: all 11 staging + 13 prod roles observed live 2026-07-16 (Pass-12).</t>
+          <t>Smoke-only if time permits: all 11 staging + 13 prod roles observed live (Pass-12, consolidated 2026-07-16; some staging role cells reuse 2026-07-15 captures — Parts Technician's is flagged for re-observe in GAP-09).</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -5197,7 +5207,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>The workbook READ ME labels these staging cells as method-derived: "New Payment reachable (Take Payment observed SHOWN); org-device gate satisfied" — the button itself was pixel-observed for the invoicing-role set, and derived from the reachable New Payment dialog for these 3. Re-observe directly on the release build.</t>
+          <t>The ground-truth workbook's "Send to Terminal LIVE" tab labels these 3 staging cells as method-derived: "New Payment reachable (Take Payment observed SHOWN); org-device gate satisfied" — the button itself was pixel-observed only for the invoicing-role set (SendToTerminal_dialog.png exists for Admin/Service Manager/Senior Service Advisor/Service Advisor/Parts Manager, not for these 3), and derived from the reachable New Payment dialog for these 3. Re-observe directly on the release build.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -5212,7 +5222,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>build/custom-roles-run/live-ui-2026-07-16/ (Pass-12 SendToTerminal_dialog.png set)</t>
+          <t>build/custom-roles-run/live-ui-2026-07-15/staging/*/SendToTerminal_dialog.png (pixel-observed roles only) + build/custom-roles-run/live-ui-2026-07-16/production/_terminal (Pass-12 org-gate captures)</t>
         </is>
       </c>
     </row>
